--- a/Schematic/bom.xlsx
+++ b/Schematic/bom.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="bom" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="86">
   <si>
     <t>Reference</t>
   </si>
@@ -259,12 +259,33 @@
   </si>
   <si>
     <t>Ibadan</t>
+  </si>
+  <si>
+    <t>Unit Price (₦)</t>
+  </si>
+  <si>
+    <t>Total Price (₦)</t>
+  </si>
+  <si>
+    <t>Tactile Switch Caps</t>
+  </si>
+  <si>
+    <t>Potentiometer Knob</t>
+  </si>
+  <si>
+    <t>Potentiometer Knob Cap</t>
+  </si>
+  <si>
+    <t>Veroboard</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="6" formatCode="&quot;₦&quot;#,##0;[Red]\-&quot;₦&quot;#,##0"/>
+  </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -770,12 +791,18 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1100,7 +1127,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60" style="1" customWidth="1"/>
@@ -1108,10 +1135,12 @@
     <col min="3" max="3" width="14.85546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="35.85546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="6" width="13.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
@@ -1127,8 +1156,14 @@
       <c r="E1" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>38</v>
       </c>
@@ -1144,8 +1179,15 @@
       <c r="E2" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="3">
+        <v>80</v>
+      </c>
+      <c r="G2" s="3">
+        <f>C2*F2</f>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
@@ -1161,8 +1203,15 @@
       <c r="E3" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="3">
+        <v>35</v>
+      </c>
+      <c r="G3" s="3">
+        <f>C3*F3</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>26</v>
       </c>
@@ -1178,498 +1227,731 @@
       <c r="E4" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="3">
+        <v>45</v>
+      </c>
+      <c r="G4" s="3">
+        <f t="shared" ref="G4:G27" si="0">C4*F4</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>76</v>
+      <c r="D5" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="F5" s="3">
+        <v>300</v>
+      </c>
+      <c r="G5" s="3">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="3">
+        <v>300</v>
+      </c>
+      <c r="G6" s="3">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>78</v>
+      <c r="D7" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="F7" s="3">
+        <v>35</v>
+      </c>
+      <c r="G7" s="3">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="3">
+        <v>350</v>
+      </c>
+      <c r="G8" s="3">
+        <f t="shared" si="0"/>
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="3">
+        <v>35</v>
+      </c>
+      <c r="G9" s="3">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="3">
+        <v>35</v>
+      </c>
+      <c r="G10" s="3">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C11" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" s="3">
+        <v>45</v>
+      </c>
+      <c r="G11" s="3">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="3">
+        <v>280</v>
+      </c>
+      <c r="G12" s="3">
+        <f t="shared" si="0"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="3">
+        <v>80</v>
+      </c>
+      <c r="G13" s="3">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="3">
+        <v>45</v>
+      </c>
+      <c r="G14" s="3">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="1">
         <v>2</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="1">
-        <v>2</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="1">
-        <v>2</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="1">
+      <c r="D15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="3">
+        <v>300</v>
+      </c>
+      <c r="G15" s="3">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="1">
         <v>1</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="1">
-        <v>3</v>
-      </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" s="3">
+        <v>6600</v>
+      </c>
+      <c r="G16" s="3">
+        <f t="shared" si="0"/>
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1">
         <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G17" s="3">
+        <f t="shared" si="0"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C18" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="3">
+        <v>4600</v>
+      </c>
+      <c r="G18" s="3">
+        <f t="shared" si="0"/>
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C19" s="1">
         <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G19" s="3">
+        <f t="shared" si="0"/>
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1">
         <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G20" s="3">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C21" s="1">
         <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="3">
+        <v>300</v>
+      </c>
+      <c r="G21" s="3">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="3">
+        <v>200</v>
+      </c>
+      <c r="G22" s="3">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C23" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="3">
+        <v>70</v>
+      </c>
+      <c r="G23" s="3">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="1">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G25" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="1">
-        <v>1</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>78</v>
+      <c r="C26" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G26" s="3">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C27" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27" s="3">
+        <v>350</v>
+      </c>
+      <c r="G27" s="3">
+        <f t="shared" si="0"/>
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C28" s="1">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>78</v>
+        <v>10</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="F28" s="3">
+        <v>90</v>
+      </c>
+      <c r="G28" s="3">
+        <f>C28*F28</f>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>71</v>
+      <c r="C29" s="1">
+        <v>1</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="G29" s="3"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>70</v>
+      <c r="C30" s="1">
+        <v>1</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="F30" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>74</v>
+      <c r="C31" s="1">
+        <v>3</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31" s="3">
+        <v>500</v>
+      </c>
+      <c r="G31" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G32" s="3"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="1">
-        <v>5</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" s="1" t="s">
+      <c r="C34" s="1">
+        <v>3</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F34" s="3">
+        <v>45</v>
+      </c>
+      <c r="G34" s="3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="1">
-        <v>10</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>62</v>
+      <c r="C35" s="1">
+        <v>2</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F35" s="3">
+        <v>200</v>
+      </c>
+      <c r="G35" s="3">
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -1677,31 +1959,35 @@
     <hyperlink ref="D2" r:id="rId1"/>
     <hyperlink ref="D3" r:id="rId2"/>
     <hyperlink ref="D4" r:id="rId3"/>
-    <hyperlink ref="D8" r:id="rId4"/>
-    <hyperlink ref="D9" r:id="rId5"/>
-    <hyperlink ref="D10" r:id="rId6"/>
-    <hyperlink ref="D11" r:id="rId7"/>
+    <hyperlink ref="D5" r:id="rId4"/>
+    <hyperlink ref="D6" r:id="rId5"/>
+    <hyperlink ref="D7" r:id="rId6"/>
+    <hyperlink ref="D12" r:id="rId7"/>
     <hyperlink ref="D13" r:id="rId8"/>
-    <hyperlink ref="D12" r:id="rId9"/>
-    <hyperlink ref="D14" r:id="rId10"/>
-    <hyperlink ref="D15" r:id="rId11"/>
-    <hyperlink ref="D16" r:id="rId12"/>
-    <hyperlink ref="D17" r:id="rId13"/>
-    <hyperlink ref="D18" r:id="rId14"/>
-    <hyperlink ref="D19" r:id="rId15"/>
-    <hyperlink ref="D20" r:id="rId16"/>
-    <hyperlink ref="D22" r:id="rId17"/>
-    <hyperlink ref="D23" r:id="rId18"/>
-    <hyperlink ref="D24" r:id="rId19"/>
-    <hyperlink ref="D25" r:id="rId20"/>
-    <hyperlink ref="D21" r:id="rId21"/>
-    <hyperlink ref="D27" r:id="rId22"/>
-    <hyperlink ref="D32" r:id="rId23"/>
-    <hyperlink ref="D33" r:id="rId24"/>
-    <hyperlink ref="D29" r:id="rId25"/>
-    <hyperlink ref="D30" r:id="rId26"/>
-    <hyperlink ref="D31" r:id="rId27"/>
+    <hyperlink ref="D14" r:id="rId9"/>
+    <hyperlink ref="D15" r:id="rId10"/>
+    <hyperlink ref="D16" r:id="rId11"/>
+    <hyperlink ref="D17" r:id="rId12"/>
+    <hyperlink ref="D18" r:id="rId13"/>
+    <hyperlink ref="D20" r:id="rId14"/>
+    <hyperlink ref="D21" r:id="rId15"/>
+    <hyperlink ref="D22" r:id="rId16"/>
+    <hyperlink ref="D23" r:id="rId17"/>
+    <hyperlink ref="D27" r:id="rId18"/>
+    <hyperlink ref="D28" r:id="rId19"/>
+    <hyperlink ref="D24" r:id="rId20"/>
+    <hyperlink ref="D25" r:id="rId21"/>
+    <hyperlink ref="D26" r:id="rId22"/>
+    <hyperlink ref="D34" r:id="rId23"/>
+    <hyperlink ref="D35" r:id="rId24"/>
+    <hyperlink ref="D31" r:id="rId25"/>
+    <hyperlink ref="D11" r:id="rId26"/>
+    <hyperlink ref="D10" r:id="rId27"/>
+    <hyperlink ref="D8" r:id="rId28" display="10k Resistor"/>
+    <hyperlink ref="D9" r:id="rId29"/>
+    <hyperlink ref="D19" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId31"/>
 </worksheet>
 </file>
--- a/Schematic/bom.xlsx
+++ b/Schematic/bom.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="88">
   <si>
     <t>Reference</t>
   </si>
@@ -277,6 +277,12 @@
   </si>
   <si>
     <t>Veroboard</t>
+  </si>
+  <si>
+    <t>19V AC-DC Adapter</t>
+  </si>
+  <si>
+    <t>Compudel</t>
   </si>
 </sst>
 </file>
@@ -1127,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60" style="1" customWidth="1"/>
@@ -1952,6 +1958,29 @@
       </c>
       <c r="G35" s="3">
         <v>400</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F36" s="3">
+        <v>8700</v>
+      </c>
+      <c r="G36" s="3">
+        <v>8700</v>
       </c>
     </row>
   </sheetData>
